--- a/QCM1_3_PHY.xlsx
+++ b/QCM1_3_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EE160F-8741-4CBB-A463-B2880418D1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42E02E9-E4E9-4E1C-9022-2C5652861CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -401,10 +401,6 @@
 Une onde harmonique se propage le long d'une corde. Les dessins ci-contre donnent la forme de la corde aux temps $t=0\text{ s}$ et $t=0,2\text{ s}$.</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Onde ultrasonore et 3 récepteurs : &lt;/b&gt;&lt;/center&gt;
-Un dispositif émet une onde ultrasonore qui se propage dans l'air jusqu'à trois récepteurs $R_1$, $R_2$ et $R_3$. Les récepteurs sont reliés à un oscilloscope. On repère les positions par rapport à l'émetteur ($x_1 &lt; x_2 &lt; x_3$). La sensibilité est $1\text{ mV/div}$ (vertical) et $12,5\text{ \mu s/div}$ (horizontal).</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Une corde horizontale : &lt;/b&gt;&lt;/center&gt;
 Une corde horizontale, supposée infinie, est soumise à un ébranlement transversal sinusoïdal à partir de son extrémité O. L'origine des temps est prise lorsque O passe par sa position d'équilibre en allant vers le haut. Sa fréquence est de $100\text{ Hz}$ et son amplitude de $1\text{ mm}$. Il se propage dans le sens positif, de la gauche vers la droite, avec une célérité de $5\text{ m.s}^{-1}$. Les amplitudes $y$ sont exprimées en mm.</t>
   </si>
@@ -463,6 +459,10 @@
   </si>
   <si>
     <t>$680\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Onde ultrasonore et 3 récepteurs : &lt;/b&gt;&lt;/center&gt;
+Un dispositif émet une onde ultrasonore qui se propage dans l'air jusqu'à trois récepteurs $R_1$, $R_2$ et $R_3$. Les récepteurs sont reliés à un oscilloscope. On repère les positions par rapport à l'émetteur ($x_1 &lt; x_2 &lt; x_3$). La sensibilité est $1\text{ mV/div}$ (vertical) et $12,5 \, \mu \text{s/div}$ (horizontal).</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K2" s="5"/>
     </row>
@@ -1079,7 +1079,7 @@
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K4" s="5"/>
     </row>
@@ -1112,13 +1112,13 @@
         <v>31</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>35</v>
@@ -1143,7 +1143,7 @@
         <v>38</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K6" s="5"/>
     </row>
@@ -1183,22 +1183,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1235,7 +1235,7 @@
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
@@ -1293,7 +1293,7 @@
     <row r="12" spans="1:11" ht="102" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>3</v>
@@ -1315,7 +1315,7 @@
         <v>60</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K12" s="5"/>
     </row>
@@ -1346,14 +1346,14 @@
         <v>65</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>3</v>
@@ -1362,7 +1362,7 @@
         <v>70</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>71</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="15" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>73</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>89</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="24" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>104</v>
@@ -1642,7 +1642,7 @@
         <v>106</v>
       </c>
       <c r="J24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">

--- a/QCM1_3_PHY.xlsx
+++ b/QCM1_3_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42E02E9-E4E9-4E1C-9022-2C5652861CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A09668-0F87-48FB-935D-0341902EA921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="144">
   <si>
     <t>Question</t>
   </si>
@@ -217,9 +217,6 @@
   </si>
   <si>
     <t>Écran D</t>
-  </si>
-  <si>
-    <t>Parmi les propositions suivantes, laquelle pourrait donner l'écran d'oscilloscope qui suit :</t>
   </si>
   <si>
     <t>$x_1=20\text{ cm}, x_2=32\text{ cm}, x_3=40\text{ cm}$</t>
@@ -434,9 +431,6 @@
     <t>PHY_QCM1_1_Q14.png</t>
   </si>
   <si>
-    <t>PHY_QCM1_1_Q15.png; PHY_QCM1_1_Q16.png</t>
-  </si>
-  <si>
     <t>PHY_QCM1_1_Q17.png</t>
   </si>
   <si>
@@ -463,6 +457,15 @@
   <si>
     <t>&lt;center&gt;&lt;b&gt;Onde ultrasonore et 3 récepteurs : &lt;/b&gt;&lt;/center&gt;
 Un dispositif émet une onde ultrasonore qui se propage dans l'air jusqu'à trois récepteurs $R_1$, $R_2$ et $R_3$. Les récepteurs sont reliés à un oscilloscope. On repère les positions par rapport à l'émetteur ($x_1 &lt; x_2 &lt; x_3$). La sensibilité est $1\text{ mV/div}$ (vertical) et $12,5 \, \mu \text{s/div}$ (horizontal).</t>
+  </si>
+  <si>
+    <t>Parmi les 4 propositions suivantes, laquelle pourrait donner l'écran d'oscilloscope qui suit :</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_1_Q15.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_1_Q16.png</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1020,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K2" s="5"/>
     </row>
@@ -1052,7 +1055,7 @@
     </row>
     <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>25</v>
@@ -1079,13 +1082,13 @@
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>30</v>
@@ -1112,13 +1115,13 @@
         <v>31</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>35</v>
@@ -1143,7 +1146,7 @@
         <v>38</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K6" s="5"/>
     </row>
@@ -1171,7 +1174,9 @@
       <c r="I7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="13"/>
+      <c r="J7" s="13" t="s">
+        <v>143</v>
+      </c>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1183,22 +1188,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1235,7 +1240,7 @@
     <row r="10" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
@@ -1293,7 +1298,7 @@
     <row r="12" spans="1:11" ht="102" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>3</v>
@@ -1315,95 +1320,95 @@
         <v>60</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="I13" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>56</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1411,26 +1416,26 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -1438,265 +1443,265 @@
     <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>80</v>
-      </c>
       <c r="F17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="E20" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="I24" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="I25" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="H26" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="I26" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
